--- a/modelo_importacao_mpleao.xlsx
+++ b/modelo_importacao_mpleao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\SISTEMA_MPLEAO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1341F86D-41B5-42FA-BD94-194959C66491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C9BEF3-4E25-487E-BC6B-E296821BE642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="IMPORTAÇÃO" sheetId="1" r:id="rId1"/>
     <sheet name="INSTRUÇÕES" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -178,7 +178,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +239,12 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -309,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -355,6 +361,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,9 +677,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -775,41 +790,47 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5">
+        <v>100</v>
+      </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5">
+        <v>100</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5">
+        <v>100</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
